--- a/LISTAS/mi/CORTINA Y PROTECTOR DE BAÑO DISMAY.xlsx
+++ b/LISTAS/mi/CORTINA Y PROTECTOR DE BAÑO DISMAY.xlsx
@@ -911,16 +911,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45163.60863264077</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="28" t="n"/>
     </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -963,17 +960,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -1054,7 +1040,6 @@
       <c r="F30" s="47" t="n"/>
       <c r="G30" s="47" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="17">
       <c r="A32" s="31" t="n"/>
       <c r="B32" s="31" t="n"/>
@@ -1067,21 +1052,15 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" s="17"/>
     <row r="35" ht="16.5" customHeight="1" s="17"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39" ht="19.5" customHeight="1" s="17">
       <c r="A39" s="7" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="5" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="6" t="n"/>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1092,13 +1071,13 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/LISTAS/mi/CORTINA Y PROTECTOR DE BAÑO DISMAY.xlsx
+++ b/LISTAS/mi/CORTINA Y PROTECTOR DE BAÑO DISMAY.xlsx
@@ -911,7 +911,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/CORTINA Y PROTECTOR DE BAÑO DISMAY.xlsx
+++ b/LISTAS/mi/CORTINA Y PROTECTOR DE BAÑO DISMAY.xlsx
@@ -911,7 +911,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/CORTINA Y PROTECTOR DE BAÑO DISMAY.xlsx
+++ b/LISTAS/mi/CORTINA Y PROTECTOR DE BAÑO DISMAY.xlsx
@@ -911,13 +911,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45266</v>
+        <v>45163.60863264077</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="28" t="n"/>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -960,6 +963,17 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -1040,6 +1054,7 @@
       <c r="F30" s="47" t="n"/>
       <c r="G30" s="47" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="17">
       <c r="A32" s="31" t="n"/>
       <c r="B32" s="31" t="n"/>
@@ -1052,15 +1067,21 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" s="17"/>
     <row r="35" ht="16.5" customHeight="1" s="17"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
     <row r="39" ht="19.5" customHeight="1" s="17">
       <c r="A39" s="7" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="5" t="n"/>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="6" t="n"/>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1071,13 +1092,13 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/LISTAS/mi/CORTINA Y PROTECTOR DE BAÑO DISMAY.xlsx
+++ b/LISTAS/mi/CORTINA Y PROTECTOR DE BAÑO DISMAY.xlsx
@@ -911,16 +911,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45163.60863264077</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="28" t="n"/>
     </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -963,17 +960,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -1054,7 +1040,6 @@
       <c r="F30" s="47" t="n"/>
       <c r="G30" s="47" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="17">
       <c r="A32" s="31" t="n"/>
       <c r="B32" s="31" t="n"/>
@@ -1067,21 +1052,15 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" s="17"/>
     <row r="35" ht="16.5" customHeight="1" s="17"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39" ht="19.5" customHeight="1" s="17">
       <c r="A39" s="7" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="5" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="6" t="n"/>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1091,15 +1070,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
